--- a/experiments/04_lora_finetuning/report/best_models.xlsx
+++ b/experiments/04_lora_finetuning/report/best_models.xlsx
@@ -541,17 +541,17 @@
   <dimension ref="A1:K5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="11" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="8" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
-    <col width="16" customWidth="1" min="8" max="8"/>
-    <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="19" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="8" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
     <col width="16" customWidth="1" min="10" max="10"/>
-    <col width="16" customWidth="1" min="11" max="11"/>
+    <col width="19" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">

--- a/experiments/04_lora_finetuning/report/best_models.xlsx
+++ b/experiments/04_lora_finetuning/report/best_models.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="best_models" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -562,7 +562,7 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>qwen_lora_7b_no_shots_2_epochs</t>
+          <t>qwen_lora_7b_zero_shot_2_epochs</t>
         </is>
       </c>
       <c r="C1" s="2" t="n"/>
@@ -571,7 +571,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>gpt_4o_mini_few_shots</t>
+          <t>GPT-4o-mini</t>
         </is>
       </c>
       <c r="H1" s="2" t="n"/>

--- a/experiments/04_lora_finetuning/report/best_models.xlsx
+++ b/experiments/04_lora_finetuning/report/best_models.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -26,8 +26,17 @@
       <scheme val="minor"/>
     </font>
     <font/>
+    <font>
+      <color rgb="009C0006"/>
+    </font>
+    <font>
+      <color rgb="00006100"/>
+    </font>
+    <font>
+      <color rgb="009C6500"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -36,20 +45,26 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFD9D9D9"/>
-        <bgColor rgb="FFD9D9D9"/>
+        <fgColor rgb="00D9D9D9"/>
+        <bgColor rgb="00D9D9D9"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor rgb="FFFFFF00"/>
+        <fgColor rgb="00FFC7CE"/>
+        <bgColor rgb="00FFC7CE"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF00B050"/>
-        <bgColor rgb="FF00B050"/>
+        <fgColor rgb="00C6EFCE"/>
+        <bgColor rgb="00C6EFCE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFEB9C"/>
+        <bgColor rgb="00FFEB9C"/>
       </patternFill>
     </fill>
   </fills>
@@ -156,7 +171,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -167,10 +182,13 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -687,7 +705,7 @@
       <c r="E4" s="6" t="n">
         <v>0.9074</v>
       </c>
-      <c r="F4" s="7" t="n">
+      <c r="F4" s="8" t="n">
         <v>0.8070000000000001</v>
       </c>
       <c r="G4" s="6" t="n">
@@ -702,7 +720,7 @@
       <c r="J4" s="7" t="n">
         <v>0.9086</v>
       </c>
-      <c r="K4" s="7" t="n">
+      <c r="K4" s="8" t="n">
         <v>0.8070000000000001</v>
       </c>
     </row>

--- a/experiments/04_lora_finetuning/report/best_models.xlsx
+++ b/experiments/04_lora_finetuning/report/best_models.xlsx
@@ -185,10 +185,10 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -665,25 +665,25 @@
       <c r="D3" s="6" t="n">
         <v>55.58</v>
       </c>
-      <c r="E3" s="6" t="n">
+      <c r="E3" s="7" t="n">
         <v>0.8966</v>
       </c>
       <c r="F3" s="6" t="n">
         <v>0.7993</v>
       </c>
-      <c r="G3" s="7" t="n">
+      <c r="G3" s="8" t="n">
         <v>47.83</v>
       </c>
-      <c r="H3" s="7" t="n">
+      <c r="H3" s="8" t="n">
         <v>73.75</v>
       </c>
-      <c r="I3" s="7" t="n">
+      <c r="I3" s="8" t="n">
         <v>61.59</v>
       </c>
       <c r="J3" s="7" t="n">
         <v>0.9005</v>
       </c>
-      <c r="K3" s="7" t="n">
+      <c r="K3" s="8" t="n">
         <v>0.8083</v>
       </c>
     </row>
@@ -693,19 +693,19 @@
           <t>enes</t>
         </is>
       </c>
-      <c r="B4" s="7" t="n">
+      <c r="B4" s="8" t="n">
         <v>62.24</v>
       </c>
-      <c r="C4" s="7" t="n">
+      <c r="C4" s="8" t="n">
         <v>81.27</v>
       </c>
       <c r="D4" s="6" t="n">
         <v>86.13</v>
       </c>
-      <c r="E4" s="6" t="n">
+      <c r="E4" s="7" t="n">
         <v>0.9074</v>
       </c>
-      <c r="F4" s="8" t="n">
+      <c r="F4" s="7" t="n">
         <v>0.8070000000000001</v>
       </c>
       <c r="G4" s="6" t="n">
@@ -714,13 +714,13 @@
       <c r="H4" s="6" t="n">
         <v>77.91</v>
       </c>
-      <c r="I4" s="7" t="n">
+      <c r="I4" s="8" t="n">
         <v>89.31</v>
       </c>
       <c r="J4" s="7" t="n">
         <v>0.9086</v>
       </c>
-      <c r="K4" s="8" t="n">
+      <c r="K4" s="7" t="n">
         <v>0.8070000000000001</v>
       </c>
     </row>
@@ -730,16 +730,16 @@
           <t>enru</t>
         </is>
       </c>
-      <c r="B5" s="7" t="n">
+      <c r="B5" s="8" t="n">
         <v>45.69</v>
       </c>
-      <c r="C5" s="7" t="n">
+      <c r="C5" s="8" t="n">
         <v>71.62</v>
       </c>
       <c r="D5" s="6" t="n">
         <v>67.84</v>
       </c>
-      <c r="E5" s="6" t="n">
+      <c r="E5" s="7" t="n">
         <v>0.8836000000000001</v>
       </c>
       <c r="F5" s="7" t="n">
@@ -751,13 +751,13 @@
       <c r="H5" s="6" t="n">
         <v>68.09</v>
       </c>
-      <c r="I5" s="7" t="n">
+      <c r="I5" s="8" t="n">
         <v>73.51000000000001</v>
       </c>
       <c r="J5" s="7" t="n">
         <v>0.8915999999999999</v>
       </c>
-      <c r="K5" s="6" t="n">
+      <c r="K5" s="7" t="n">
         <v>0.7043</v>
       </c>
     </row>
